--- a/PAMF_DIG F2 - monthly2026-07-23.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-23.xlsx
@@ -1436,7 +1436,7 @@
         <v>0.09</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>0.09</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>0.09</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>0.09</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>0.09</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>0.09</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>0.09</v>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>0.09</v>
       </c>
       <c r="N115" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>0.09</v>
       </c>
       <c r="N120" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>0.09</v>
       </c>
       <c r="N185" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>0.09</v>
       </c>
       <c r="N216" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>0.09</v>
       </c>
       <c r="N223" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>0.09</v>
       </c>
       <c r="N309" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>0.09</v>
       </c>
       <c r="N317" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>0.09</v>
       </c>
       <c r="N373" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O373" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>0.09</v>
       </c>
       <c r="N384" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>0.09</v>
       </c>
       <c r="N403" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-23.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-23.xlsx
@@ -633,7 +633,7 @@
         <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>0.09</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>0.09</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>0.09</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>0.09</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>0.09</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>0.09</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>0.09</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>0.09</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>0.09</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>0.09</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>0.09</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>0.09</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>0.09</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>0.09</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>0.09</v>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0.09</v>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>0.09</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>0.09</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>0.09</v>
       </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>0.09</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>0.09</v>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>0.09</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>0.09</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>0.09</v>
       </c>
       <c r="N113" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>0.09</v>
       </c>
       <c r="N116" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>0.09</v>
       </c>
       <c r="N121" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>0.09</v>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>0.09</v>
       </c>
       <c r="N125" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>0.09</v>
       </c>
       <c r="N138" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>0.09</v>
       </c>
       <c r="N141" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>0.09</v>
       </c>
       <c r="N146" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>0.09</v>
       </c>
       <c r="N158" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>0.09</v>
       </c>
       <c r="N160" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>0.09</v>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>0.09</v>
       </c>
       <c r="N163" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>0.09</v>
       </c>
       <c r="N165" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>0.09</v>
       </c>
       <c r="N166" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>0.09</v>
       </c>
       <c r="N169" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>0.09</v>
       </c>
       <c r="N174" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>0.09</v>
       </c>
       <c r="N191" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>0.09</v>
       </c>
       <c r="N196" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>0.09</v>
       </c>
       <c r="N198" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>0.09</v>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>0.09</v>
       </c>
       <c r="N205" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>0.09</v>
       </c>
       <c r="N212" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>0.09</v>
       </c>
       <c r="N217" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>0.09</v>
       </c>
       <c r="N221" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>0.09</v>
       </c>
       <c r="N222" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>0.09</v>
       </c>
       <c r="N245" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>0.09</v>
       </c>
       <c r="N246" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>0.09</v>
       </c>
       <c r="N247" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>0.09</v>
       </c>
       <c r="N251" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>0.09</v>
       </c>
       <c r="N254" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>0.09</v>
       </c>
       <c r="N256" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>0.09</v>
       </c>
       <c r="N263" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>0.09</v>
       </c>
       <c r="N269" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>0.09</v>
       </c>
       <c r="N275" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>0.09</v>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>0.09</v>
       </c>
       <c r="N279" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>0.09</v>
       </c>
       <c r="N280" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>0.09</v>
       </c>
       <c r="N285" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>0.09</v>
       </c>
       <c r="N287" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>0.09</v>
       </c>
       <c r="N293" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>0.09</v>
       </c>
       <c r="N297" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>0.09</v>
       </c>
       <c r="N304" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>0.09</v>
       </c>
       <c r="N318" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>0.09</v>
       </c>
       <c r="N322" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>0.09</v>
       </c>
       <c r="N326" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>0.09</v>
       </c>
       <c r="N328" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>0.09</v>
       </c>
       <c r="N331" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O331" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>0.09</v>
       </c>
       <c r="N336" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>0.09</v>
       </c>
       <c r="N340" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>0.09</v>
       </c>
       <c r="N344" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>0.09</v>
       </c>
       <c r="N349" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>0.09</v>
       </c>
       <c r="N352" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>0.09</v>
       </c>
       <c r="N358" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>0.09</v>
       </c>
       <c r="N361" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>0.09</v>
       </c>
       <c r="N362" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>0.09</v>
       </c>
       <c r="N364" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>0.09</v>
       </c>
       <c r="N376" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O376" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>0.09</v>
       </c>
       <c r="N377" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O377" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>0.09</v>
       </c>
       <c r="N386" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O386" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>0.09</v>
       </c>
       <c r="N413" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
